--- a/buku-tahfidz-lengkap/versi 3 (campur tahsin)/Mentahan/ziyadah.xlsx
+++ b/buku-tahfidz-lengkap/versi 3 (campur tahsin)/Mentahan/ziyadah.xlsx
@@ -278,7 +278,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,20 +325,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -505,7 +491,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,12 +561,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1027,137 +1007,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1236,24 +1216,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1266,16 +1237,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1284,19 +1249,25 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1305,34 +1276,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1365,7 +1336,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1710,262 +1681,262 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="66"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="56" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="56" t="s">
+      <c r="D2" s="54"/>
+      <c r="E2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="57"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="66"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:6">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="69"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="66"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:6">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="69"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="66"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:6">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="69"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="66"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:6">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="69"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="66"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:6">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="69"/>
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="66"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:6">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="66"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:6">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="66"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:6">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="66"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:6">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
+      <c r="A14" s="68"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="69"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:6">
-      <c r="A15" s="68"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="66"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:6">
-      <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:18">
-      <c r="A17" s="68"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:18">
-      <c r="A18" s="68"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="66"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:18">
-      <c r="A19" s="68"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:18">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
+      <c r="A20" s="68"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:18">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
+      <c r="A21" s="65"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:18">
-      <c r="A22" s="68"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
+      <c r="A22" s="65"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:18">
-      <c r="A23" s="68"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:18">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
+      <c r="A24" s="65"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:18">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69"/>
-      <c r="R25" s="50"/>
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
+      <c r="R25" s="47"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:18">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:18">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:18">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
+      <c r="A28" s="65"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:18">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="66"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:18">
-      <c r="A30" s="68"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:18">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
+      <c r="A31" s="65"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="66"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:18">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1997,331 +1968,331 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:6">
-      <c r="A1" s="67"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67" t="s">
+      <c r="A1" s="64"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:6">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="56" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58" t="s">
+      <c r="D2" s="54"/>
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="55" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:6">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="70" t="s">
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="70"/>
+      <c r="F3" s="67"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:6">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="70" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="70"/>
+      <c r="F4" s="67"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="70" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="70"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:6">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="70" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="70"/>
+      <c r="F6" s="67"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:6">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="70"/>
+      <c r="F7" s="67"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="73" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="74"/>
+      <c r="F8" s="71"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:6">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="70" t="s">
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="70"/>
+      <c r="F9" s="67"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:6">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="70" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="70"/>
+      <c r="F10" s="67"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:6">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="70"/>
+      <c r="F11" s="67"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:6">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="70" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="70"/>
+      <c r="F12" s="67"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:6">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="70" t="s">
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="70"/>
+      <c r="F13" s="67"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:6">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="73" t="s">
+      <c r="A14" s="68"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="74"/>
+      <c r="F14" s="71"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:6">
-      <c r="A15" s="68"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="70" t="s">
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="70"/>
+      <c r="F15" s="67"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:6">
-      <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="70" t="s">
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="70"/>
+      <c r="F16" s="67"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:18">
-      <c r="A17" s="68"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="70" t="s">
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="70"/>
+      <c r="F17" s="67"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:18">
-      <c r="A18" s="68"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="70" t="s">
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="70"/>
+      <c r="F18" s="67"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:18">
-      <c r="A19" s="68"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="70" t="s">
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="70"/>
+      <c r="F19" s="67"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:18">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="73" t="s">
+      <c r="A20" s="68"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="74"/>
+      <c r="F20" s="71"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:18">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="70" t="s">
+      <c r="A21" s="65"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="70"/>
+      <c r="F21" s="67"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:18">
-      <c r="A22" s="68"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="70" t="s">
+      <c r="A22" s="65"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="70"/>
+      <c r="F22" s="67"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:18">
-      <c r="A23" s="68"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="70" t="s">
+      <c r="A23" s="65"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="70"/>
+      <c r="F23" s="67"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:18">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="70" t="s">
+      <c r="A24" s="65"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="70"/>
+      <c r="F24" s="67"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:18">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70" t="s">
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="70"/>
-      <c r="R25" s="50"/>
+      <c r="F25" s="67"/>
+      <c r="R25" s="47"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:18">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="73" t="s">
+      <c r="A26" s="68"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="74"/>
+      <c r="F26" s="71"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:18">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="70" t="s">
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="F27" s="70"/>
+      <c r="F27" s="67"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:18">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="70" t="s">
+      <c r="A28" s="65"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="70"/>
+      <c r="F28" s="67"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:18">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="70" t="s">
+      <c r="A29" s="65"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="70"/>
+      <c r="F29" s="67"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:18">
-      <c r="A30" s="68"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="70" t="s">
+      <c r="A30" s="65"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="70"/>
+      <c r="F30" s="67"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:18">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="70" t="s">
+      <c r="A31" s="65"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="70"/>
+      <c r="F31" s="67"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:18">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="73" t="s">
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="74"/>
+      <c r="F32" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2363,589 +2334,589 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67" t="s">
+      <c r="C1" s="63"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:14">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="56" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="56" t="s">
+      <c r="D2" s="54"/>
+      <c r="E2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="G2" s="56" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="57"/>
-      <c r="I2" s="56" t="s">
+      <c r="H2" s="54"/>
+      <c r="I2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="56" t="s">
+      <c r="J2" s="54"/>
+      <c r="K2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="58" t="s">
+      <c r="L2" s="54"/>
+      <c r="M2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="58" t="s">
+      <c r="N2" s="55" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:14">
-      <c r="A3" s="68"/>
-      <c r="B3" s="69"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="70" t="s">
+      <c r="A3" s="65"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="65"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="70"/>
+      <c r="N3" s="67"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:14">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="70" t="s">
+      <c r="A4" s="65"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="70"/>
+      <c r="N4" s="67"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:14">
-      <c r="A5" s="68"/>
-      <c r="B5" s="69"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="69"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="70" t="s">
+      <c r="A5" s="65"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N5" s="70"/>
+      <c r="N5" s="67"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:14">
-      <c r="A6" s="68"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="69"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="70" t="s">
+      <c r="A6" s="65"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="70"/>
+      <c r="N6" s="67"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:14">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="70" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="66"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="66"/>
+      <c r="M7" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="70"/>
+      <c r="N7" s="67"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:14">
-      <c r="A8" s="71"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="71"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="71"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="73" t="s">
+      <c r="A8" s="68"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="74"/>
+      <c r="N8" s="71"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:14">
-      <c r="A9" s="68"/>
-      <c r="B9" s="69"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="69"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="70" t="s">
+      <c r="A9" s="65"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="66"/>
+      <c r="M9" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="70"/>
+      <c r="N9" s="67"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:14">
-      <c r="A10" s="68"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="70" t="s">
+      <c r="A10" s="65"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="66"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="66"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="70"/>
+      <c r="N10" s="67"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:14">
-      <c r="A11" s="68"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="69"/>
-      <c r="M11" s="70" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N11" s="70"/>
+      <c r="N11" s="67"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:14">
-      <c r="A12" s="68"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="69"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="69"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="70" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="70"/>
+      <c r="N12" s="67"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:14">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="69"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="70" t="s">
+      <c r="A13" s="65"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="70"/>
+      <c r="N13" s="67"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:14">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="71"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="71"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="71"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="73" t="s">
+      <c r="A14" s="68"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="74"/>
+      <c r="N14" s="71"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:14">
-      <c r="A15" s="68"/>
-      <c r="B15" s="69"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="69"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="69"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="69"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="69"/>
-      <c r="M15" s="70" t="s">
+      <c r="A15" s="65"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="N15" s="70"/>
+      <c r="N15" s="67"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:14">
-      <c r="A16" s="68"/>
-      <c r="B16" s="69"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="69"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="69"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="69"/>
-      <c r="M16" s="70" t="s">
+      <c r="A16" s="65"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="66"/>
+      <c r="M16" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="N16" s="70"/>
+      <c r="N16" s="67"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:26">
-      <c r="A17" s="68"/>
-      <c r="B17" s="69"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="69"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="69"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="69"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="69"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="69"/>
-      <c r="M17" s="70" t="s">
+      <c r="A17" s="65"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="65"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N17" s="70"/>
+      <c r="N17" s="67"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:26">
-      <c r="A18" s="68"/>
-      <c r="B18" s="69"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="69"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="69"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="69"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="69"/>
-      <c r="M18" s="70" t="s">
+      <c r="A18" s="65"/>
+      <c r="B18" s="66"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="66"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="66"/>
+      <c r="M18" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="70"/>
+      <c r="N18" s="67"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:26">
-      <c r="A19" s="68"/>
-      <c r="B19" s="69"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="69"/>
-      <c r="M19" s="70" t="s">
+      <c r="A19" s="65"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N19" s="70"/>
+      <c r="N19" s="67"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:26">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="71"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="73" t="s">
+      <c r="A20" s="68"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="N20" s="74"/>
+      <c r="N20" s="71"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:26">
-      <c r="A21" s="68"/>
-      <c r="B21" s="69"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="69"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="69"/>
-      <c r="M21" s="70" t="s">
+      <c r="A21" s="65"/>
+      <c r="B21" s="66"/>
+      <c r="C21" s="65"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="65"/>
+      <c r="J21" s="66"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="66"/>
+      <c r="M21" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="N21" s="70"/>
+      <c r="N21" s="67"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:26">
-      <c r="A22" s="68"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="70" t="s">
+      <c r="A22" s="65"/>
+      <c r="B22" s="66"/>
+      <c r="C22" s="65"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="70"/>
+      <c r="N22" s="67"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:26">
-      <c r="A23" s="68"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="69"/>
-      <c r="M23" s="70" t="s">
+      <c r="A23" s="65"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="65"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N23" s="70"/>
+      <c r="N23" s="67"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:26">
-      <c r="A24" s="68"/>
-      <c r="B24" s="69"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="69"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="69"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="69"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="69"/>
-      <c r="M24" s="70" t="s">
+      <c r="A24" s="65"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N24" s="70"/>
+      <c r="N24" s="67"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:26">
-      <c r="A25" s="68"/>
-      <c r="B25" s="69"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="69"/>
-      <c r="M25" s="70" t="s">
+      <c r="A25" s="65"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N25" s="70"/>
-      <c r="Z25" s="50"/>
+      <c r="N25" s="67"/>
+      <c r="Z25" s="47"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:26">
-      <c r="A26" s="71"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="73" t="s">
+      <c r="A26" s="68"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="N26" s="74"/>
+      <c r="N26" s="71"/>
     </row>
     <row r="27" ht="18" customHeight="1" spans="1:26">
-      <c r="A27" s="68"/>
-      <c r="B27" s="69"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="69"/>
-      <c r="M27" s="70" t="s">
+      <c r="A27" s="65"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="65"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="N27" s="70"/>
+      <c r="N27" s="67"/>
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:26">
-      <c r="A28" s="68"/>
-      <c r="B28" s="69"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="69"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="69"/>
-      <c r="M28" s="70" t="s">
+      <c r="A28" s="65"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="65"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="65"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="65"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="N28" s="70"/>
+      <c r="N28" s="67"/>
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:26">
-      <c r="A29" s="68"/>
-      <c r="B29" s="69"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="69"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="69"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="69"/>
-      <c r="M29" s="70" t="s">
+      <c r="A29" s="65"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="65"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N29" s="70"/>
+      <c r="N29" s="67"/>
     </row>
     <row r="30" ht="18" customHeight="1" spans="1:26">
-      <c r="A30" s="68"/>
-      <c r="B30" s="69"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="69"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="69"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="69"/>
-      <c r="M30" s="70" t="s">
+      <c r="A30" s="65"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="65"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N30" s="70"/>
+      <c r="N30" s="67"/>
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:26">
-      <c r="A31" s="68"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="69"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="69"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="69"/>
-      <c r="M31" s="70" t="s">
+      <c r="A31" s="65"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="65"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N31" s="70"/>
+      <c r="N31" s="67"/>
     </row>
     <row r="32" ht="18" customHeight="1" spans="1:26">
-      <c r="A32" s="71"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="73" t="s">
+      <c r="A32" s="68"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="N32" s="74"/>
+      <c r="N32" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2971,72 +2942,72 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="57.8571428571429" style="51" customWidth="1"/>
-    <col min="2" max="3" width="5.71428571428571" style="51" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" style="51" customWidth="1"/>
-    <col min="5" max="5" width="6.57142857142857" style="51" customWidth="1"/>
-    <col min="6" max="6" width="4.57142857142857" style="51" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="51"/>
+    <col min="1" max="1" width="57.8571428571429" style="48" customWidth="1"/>
+    <col min="2" max="3" width="5.71428571428571" style="48" customWidth="1"/>
+    <col min="4" max="4" width="21.2857142857143" style="48" customWidth="1"/>
+    <col min="5" max="5" width="6.57142857142857" style="48" customWidth="1"/>
+    <col min="6" max="6" width="4.57142857142857" style="48" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="23.25" spans="1:4">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="62"/>
+      <c r="D3" s="59"/>
     </row>
     <row r="4" ht="66" customHeight="1" spans="1:4">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="63"/>
+      <c r="A4" s="57"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="60"/>
     </row>
     <row r="5" ht="66" customHeight="1" spans="1:4">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="64"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="61"/>
     </row>
     <row r="6" ht="66" customHeight="1" spans="1:4">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="64"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="61"/>
     </row>
     <row r="7" ht="66" customHeight="1" spans="1:4">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="65"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="62"/>
     </row>
     <row r="8" ht="66" customHeight="1" spans="1:4">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="63"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="60"/>
     </row>
     <row r="9" ht="66" customHeight="1" spans="1:4">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="64"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="61"/>
     </row>
     <row r="10" ht="66" customHeight="1" spans="1:4">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="64"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="61"/>
     </row>
     <row r="11" ht="66" customHeight="1" spans="1:4">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="65"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3059,249 +3030,249 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="4.71428571428571" style="51" customWidth="1"/>
-    <col min="2" max="2" width="8.71428571428571" style="51" customWidth="1"/>
-    <col min="3" max="4" width="8" style="51" customWidth="1"/>
-    <col min="5" max="5" width="13.2857142857143" style="51" customWidth="1"/>
-    <col min="6" max="6" width="5.71428571428571" style="51" customWidth="1"/>
-    <col min="7" max="7" width="14.7142857142857" style="51" customWidth="1"/>
-    <col min="8" max="8" width="6.57142857142857" style="51" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="51"/>
+    <col min="1" max="1" width="4.71428571428571" style="48" customWidth="1"/>
+    <col min="2" max="2" width="8.71428571428571" style="48" customWidth="1"/>
+    <col min="3" max="4" width="8" style="48" customWidth="1"/>
+    <col min="5" max="5" width="13.2857142857143" style="48" customWidth="1"/>
+    <col min="6" max="6" width="5.71428571428571" style="48" customWidth="1"/>
+    <col min="7" max="7" width="14.7142857142857" style="48" customWidth="1"/>
+    <col min="8" max="8" width="6.57142857142857" style="48" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="54"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="57"/>
-      <c r="E4" s="58" t="s">
+      <c r="D4" s="54"/>
+      <c r="E4" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="55" t="s">
+      <c r="G4" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="55" t="s">
+      <c r="H4" s="52" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="58" t="s">
+      <c r="A5" s="56"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
     </row>
     <row r="6" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
+      <c r="A6" s="57"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
     </row>
     <row r="7" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
     </row>
     <row r="8" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
     </row>
     <row r="9" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
     </row>
     <row r="10" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
     </row>
     <row r="11" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
     </row>
     <row r="12" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
     </row>
     <row r="13" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A13" s="60"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
     </row>
     <row r="14" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
     </row>
     <row r="15" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
     </row>
     <row r="16" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
     </row>
     <row r="17" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
     </row>
     <row r="18" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
     </row>
     <row r="19" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
     </row>
     <row r="20" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A20" s="60"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
     </row>
     <row r="21" ht="31.5" customHeight="1" spans="1:8">
-      <c r="A21" s="60"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3328,40 +3299,40 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4"/>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="J1" s="46" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="J2" s="49" t="s">
+      <c r="G2" s="47"/>
+      <c r="J2" s="46" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="46" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="51"/>
-      <c r="E4" s="49" t="s">
+      <c r="A4" s="48"/>
+      <c r="E4" s="46" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="E5" s="49" t="s">
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="E5" s="46" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3572,63 +3543,63 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:7">
       <c r="A19" s="27"/>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="28" t="s">
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="30"/>
+      <c r="G19" s="29"/>
     </row>
     <row r="20" ht="56" customHeight="1" spans="1:7">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
     </row>
     <row r="21" ht="56" customHeight="1" spans="1:7">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="36"/>
     </row>
     <row r="22" ht="56" customHeight="1" spans="1:7">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
     </row>
     <row r="23" ht="56" customHeight="1" spans="1:7">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="36"/>
     </row>
     <row r="24" ht="56" customHeight="1" spans="1:7">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -3722,7 +3693,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="43" t="s">
         <v>51</v>
       </c>
       <c r="F5" s="5"/>
@@ -3744,7 +3715,7 @@
       <c r="D6" s="15">
         <v>10</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="44"/>
       <c r="F6" s="5"/>
       <c r="G6" s="17" t="s">
         <v>53</v>
@@ -3774,7 +3745,7 @@
       <c r="D8" s="19"/>
       <c r="E8" s="18"/>
       <c r="F8" s="5"/>
-      <c r="G8" s="75" t="s">
+      <c r="G8" s="72" t="s">
         <v>57</v>
       </c>
       <c r="H8" s="14" t="s">
@@ -3788,7 +3759,7 @@
       <c r="D9" s="21"/>
       <c r="E9" s="20"/>
       <c r="F9" s="5"/>
-      <c r="G9" s="75" t="s">
+      <c r="G9" s="72" t="s">
         <v>59</v>
       </c>
       <c r="H9" s="14" t="s">
@@ -3802,7 +3773,7 @@
       <c r="D10" s="21"/>
       <c r="E10" s="20"/>
       <c r="F10" s="5"/>
-      <c r="G10" s="75" t="s">
+      <c r="G10" s="72" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="14" t="s">
@@ -3880,7 +3851,7 @@
       <c r="D16" s="19"/>
       <c r="E16" s="18"/>
       <c r="F16" s="5"/>
-      <c r="G16" s="75" t="s">
+      <c r="G16" s="72" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="14" t="s">
@@ -3894,7 +3865,7 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
-      <c r="G17" s="75" t="s">
+      <c r="G17" s="72" t="s">
         <v>67</v>
       </c>
       <c r="H17" s="14" t="s">
@@ -3918,17 +3889,17 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:8">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="E19" s="31"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="5"/>
       <c r="G19" s="14">
         <v>41</v>
@@ -3938,60 +3909,60 @@
       </c>
     </row>
     <row r="20" ht="56" customHeight="1" spans="1:8">
-      <c r="A20" s="33"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
     <row r="21" ht="56" customHeight="1" spans="1:8">
-      <c r="A21" s="38"/>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="41"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="43"/>
+      <c r="H21" s="38"/>
     </row>
     <row r="22" ht="56" customHeight="1" spans="1:8">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="42" t="s">
+      <c r="G22" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="43"/>
+      <c r="H22" s="38"/>
     </row>
     <row r="23" ht="56" customHeight="1" spans="1:8">
-      <c r="A23" s="38"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="H23" s="45"/>
+      <c r="H23" s="40"/>
     </row>
     <row r="24" ht="56" customHeight="1" spans="1:8">
-      <c r="A24" s="33"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="47"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -4215,7 +4186,7 @@
       <c r="K8" s="19"/>
       <c r="L8" s="18"/>
       <c r="M8" s="5"/>
-      <c r="N8" s="75" t="s">
+      <c r="N8" s="72" t="s">
         <v>57</v>
       </c>
       <c r="O8" s="14" t="s">
@@ -4236,7 +4207,7 @@
       <c r="K9" s="21"/>
       <c r="L9" s="20"/>
       <c r="M9" s="5"/>
-      <c r="N9" s="75" t="s">
+      <c r="N9" s="72" t="s">
         <v>59</v>
       </c>
       <c r="O9" s="14" t="s">
@@ -4257,7 +4228,7 @@
       <c r="K10" s="21"/>
       <c r="L10" s="20"/>
       <c r="M10" s="5"/>
-      <c r="N10" s="75" t="s">
+      <c r="N10" s="72" t="s">
         <v>61</v>
       </c>
       <c r="O10" s="14" t="s">
@@ -4377,7 +4348,7 @@
       <c r="K16" s="19"/>
       <c r="L16" s="18"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="75" t="s">
+      <c r="N16" s="72" t="s">
         <v>66</v>
       </c>
       <c r="O16" s="14" t="s">
@@ -4398,7 +4369,7 @@
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="75" t="s">
+      <c r="N17" s="72" t="s">
         <v>67</v>
       </c>
       <c r="O17" s="14" t="s">
@@ -4434,29 +4405,29 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="27"/>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="28" t="s">
+      <c r="C19" s="28"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="29" t="s">
+      <c r="F19" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="30"/>
-      <c r="H19" s="28" t="s">
+      <c r="G19" s="29"/>
+      <c r="H19" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="30" t="s">
+      <c r="I19" s="28"/>
+      <c r="J19" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="31" t="s">
+      <c r="K19" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="L19" s="31"/>
+      <c r="L19" s="23"/>
       <c r="M19" s="5"/>
       <c r="N19" s="14">
         <v>41</v>
@@ -4466,95 +4437,95 @@
       </c>
     </row>
     <row r="20" ht="43" customHeight="1" spans="1:15">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
     </row>
     <row r="21" ht="43" customHeight="1" spans="1:15">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
       <c r="M21" s="5"/>
-      <c r="N21" s="42" t="s">
+      <c r="N21" s="37" t="s">
         <v>71</v>
       </c>
-      <c r="O21" s="43"/>
+      <c r="O21" s="38"/>
     </row>
     <row r="22" ht="43" customHeight="1" spans="1:15">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
       <c r="M22" s="5"/>
-      <c r="N22" s="42" t="s">
+      <c r="N22" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="O22" s="43"/>
+      <c r="O22" s="38"/>
     </row>
     <row r="23" ht="43" customHeight="1" spans="1:15">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="41"/>
-      <c r="L23" s="41"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
       <c r="M23" s="5"/>
-      <c r="N23" s="44" t="s">
+      <c r="N23" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="O23" s="45"/>
+      <c r="O23" s="40"/>
     </row>
     <row r="24" ht="43" customHeight="1" spans="1:15">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="35"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
       <c r="M24" s="5"/>
-      <c r="N24" s="46"/>
-      <c r="O24" s="47"/>
+      <c r="N24" s="41"/>
+      <c r="O24" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="48">
